--- a/data/trans_bre/P57GLOBAL_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 15,01</t>
+          <t>4,24; 15,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 13,34</t>
+          <t>-0,07; 14,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 6,72</t>
+          <t>-5,27; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 15,18</t>
+          <t>-1,53; 15,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 19,47</t>
+          <t>5,08; 20,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,97</t>
+          <t>-0,12; 18,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 8,21</t>
+          <t>-6,0; 8,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 32,3</t>
+          <t>-2,58; 32,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 13,11</t>
+          <t>0,94; 12,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 8,34</t>
+          <t>-3,68; 8,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 4,45</t>
+          <t>-5,27; 4,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 1,11</t>
+          <t>-12,65; 1,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 22,15</t>
+          <t>1,35; 21,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 15,41</t>
+          <t>-6,16; 15,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 5,42</t>
+          <t>-6,16; 5,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 2,06</t>
+          <t>-18,71; 2,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 2,37</t>
+          <t>-13,69; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 17,53</t>
+          <t>2,81; 16,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 9,95</t>
+          <t>-1,86; 10,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 14,19</t>
+          <t>-1,23; 13,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 4,24</t>
+          <t>-20,32; 4,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 28,06</t>
+          <t>4,47; 26,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 13,24</t>
+          <t>-2,21; 13,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 32,47</t>
+          <t>-2,36; 31,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 5,63</t>
+          <t>-7,68; 5,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 15,97</t>
+          <t>2,37; 16,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 17,84</t>
+          <t>3,2; 18,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 6,6</t>
+          <t>-18,53; 4,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 8,22</t>
+          <t>-10,14; 8,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 32,26</t>
+          <t>4,14; 34,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 39,81</t>
+          <t>6,04; 41,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 21,77</t>
+          <t>-48,31; 15,36</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 12,73</t>
+          <t>-0,93; 13,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 26,01</t>
+          <t>7,06; 26,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 5,92</t>
+          <t>-4,95; 5,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,6</t>
+          <t>-5,2; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 16,91</t>
+          <t>-1,24; 17,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 50,37</t>
+          <t>11,18; 51,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 6,75</t>
+          <t>-5,21; 6,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 5,11</t>
+          <t>-5,43; 5,3</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 10,17</t>
+          <t>-5,01; 9,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 20,29</t>
+          <t>4,78; 20,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 8,97</t>
+          <t>-4,42; 9,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 7,38</t>
+          <t>-6,61; 7,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 14,96</t>
+          <t>-6,8; 14,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 33,72</t>
+          <t>7,32; 33,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 11,94</t>
+          <t>-5,17; 11,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 20,42</t>
+          <t>-14,87; 20,96</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 1,61</t>
+          <t>-10,07; 1,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,81</t>
+          <t>4,48; 14,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 7,14</t>
+          <t>-0,43; 7,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 6,03</t>
+          <t>-5,56; 5,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 3,08</t>
+          <t>-17,77; 2,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 25,16</t>
+          <t>6,83; 25,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 8,63</t>
+          <t>-0,49; 8,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 9,78</t>
+          <t>-7,96; 9,56</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,54</t>
+          <t>1,54; 8,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,7</t>
+          <t>-4,4; 1,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,49</t>
+          <t>-0,54; 4,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 61,94</t>
+          <t>1,39; 59,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,59</t>
+          <t>1,82; 10,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,91</t>
+          <t>-4,74; 1,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,9</t>
+          <t>-0,55; 4,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 234,16</t>
+          <t>1,58; 194,79</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,04</t>
+          <t>-0,39; 3,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,72</t>
+          <t>4,09; 8,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,7</t>
+          <t>1,02; 4,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 17,97</t>
+          <t>-1,83; 17,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,87</t>
+          <t>-0,54; 5,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,92</t>
+          <t>5,84; 12,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,86</t>
+          <t>1,22; 6,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 39,57</t>
+          <t>-3,05; 36,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57GLOBAL_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 15,56</t>
+          <t>3,3; 14,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 14,05</t>
+          <t>0,31; 14,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 7,03</t>
+          <t>-5,25; 7,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 15,3</t>
+          <t>-2,18; 13,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 20,17</t>
+          <t>3,88; 19,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 18,58</t>
+          <t>0,38; 19,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 8,67</t>
+          <t>-5,91; 9,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 32,7</t>
+          <t>-3,58; 25,28</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,63</t>
+          <t>-5,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,88%</t>
+          <t>-8,89%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 12,93</t>
+          <t>0,76; 12,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 8,52</t>
+          <t>-4,19; 8,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,07</t>
+          <t>-5,15; 4,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 1,39</t>
+          <t>-11,9; 1,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 21,79</t>
+          <t>1,05; 21,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 15,93</t>
+          <t>-7,02; 17,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 5,0</t>
+          <t>-6,05; 5,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 2,25</t>
+          <t>-17,75; 1,85</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 2,74</t>
+          <t>-13,03; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 16,16</t>
+          <t>3,01; 16,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 10,07</t>
+          <t>-1,68; 10,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 13,68</t>
+          <t>-0,08; 14,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 4,04</t>
+          <t>-18,96; 4,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 26,13</t>
+          <t>4,11; 26,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 13,59</t>
+          <t>-2,08; 14,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 31,09</t>
+          <t>-0,15; 32,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-14,18%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 5,75</t>
+          <t>-8,08; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 16,96</t>
+          <t>1,33; 16,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 18,1</t>
+          <t>3,35; 18,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 4,93</t>
+          <t>-4,84; 11,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 8,2</t>
+          <t>-10,68; 7,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 34,28</t>
+          <t>2,41; 32,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 41,58</t>
+          <t>6,48; 41,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 15,36</t>
+          <t>-12,54; 40,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 13,35</t>
+          <t>-1,35; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 26,51</t>
+          <t>6,24; 25,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 5,36</t>
+          <t>-5,33; 6,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 4,78</t>
+          <t>-4,04; 5,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 17,45</t>
+          <t>-1,54; 17,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 51,22</t>
+          <t>10,04; 50,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 6,09</t>
+          <t>-5,69; 6,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 5,3</t>
+          <t>-4,27; 6,38</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>-1,16%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 9,64</t>
+          <t>-4,79; 9,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 20,04</t>
+          <t>4,95; 19,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 9,05</t>
+          <t>-5,18; 8,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 7,56</t>
+          <t>-7,51; 6,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 14,24</t>
+          <t>-6,4; 14,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 33,57</t>
+          <t>7,12; 32,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 11,85</t>
+          <t>-6,23; 10,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 20,96</t>
+          <t>-16,27; 17,42</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-0,1%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 1,48</t>
+          <t>-10,16; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 14,98</t>
+          <t>4,47; 15,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,22</t>
+          <t>-0,39; 7,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 5,92</t>
+          <t>-4,85; 5,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 2,96</t>
+          <t>-17,83; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 25,43</t>
+          <t>6,59; 25,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,78</t>
+          <t>-0,44; 9,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 9,56</t>
+          <t>-6,95; 8,32</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25,11</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,72</t>
+          <t>1,32; 8,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,6</t>
+          <t>-4,46; 1,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,35</t>
+          <t>-0,49; 4,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 59,48</t>
+          <t>-1,12; 5,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,68</t>
+          <t>1,54; 10,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,75</t>
+          <t>-4,78; 1,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,75</t>
+          <t>-0,51; 4,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 194,79</t>
+          <t>-1,28; 6,69</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,91</t>
+          <t>-0,48; 4,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,57</t>
+          <t>4,12; 8,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,86</t>
+          <t>1,06; 4,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 17,47</t>
+          <t>-1,33; 3,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,68</t>
+          <t>-0,68; 5,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,8</t>
+          <t>5,89; 12,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,0</t>
+          <t>1,28; 5,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 36,75</t>
+          <t>-2,02; 5,56</t>
         </is>
       </c>
     </row>
